--- a/Daily follow_V1/Daily follow/ZPP0059.xlsx
+++ b/Daily follow_V1/Daily follow/ZPP0059.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13257" uniqueCount="2037">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13297" uniqueCount="2049">
   <si>
     <t>400914329</t>
   </si>
@@ -5951,6 +5951,42 @@
   </si>
   <si>
     <t>20260618090711214038M5410009  542 HEX1 IN                  JQ46A745G56    M_CLR_F2061A623M              062026B 011520U52J         MSY-GX36NL-U2                 000144000144FG FG-3Z9HNFCO-BZ                                                     00040091555300501  1  B</t>
+  </si>
+  <si>
+    <t>400913190</t>
+  </si>
+  <si>
+    <t>20260618192609690493M5410010</t>
+  </si>
+  <si>
+    <t>F/P-2HS-BZ</t>
+  </si>
+  <si>
+    <t>BR18_BR18_23142</t>
+  </si>
+  <si>
+    <t>18.06.2026 19:26:55</t>
+  </si>
+  <si>
+    <t>JQ46Y440G07</t>
+  </si>
+  <si>
+    <t>M_CLR_FLAT1052B609M</t>
+  </si>
+  <si>
+    <t>200059415</t>
+  </si>
+  <si>
+    <t>20V30A</t>
+  </si>
+  <si>
+    <t>MSY-JY25VF-VN1</t>
+  </si>
+  <si>
+    <t>202</t>
+  </si>
+  <si>
+    <t>20260618192609690493M5410010  542 HEX1 IN                  JQ46Y440G07    M_CLR_FLAT1052B609M           062026A 020220V30A         MSY-JY25VF-VN1                000025000025WIPF/P-2HS-BZ                                                         00040091319000201  1  A</t>
   </si>
   <si>
     <t>Order</t>
@@ -6238,7 +6274,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:BE331"/>
+  <dimension ref="A1:BE332"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" bestFit="1" width="11" customWidth="1"/>
@@ -6302,175 +6338,175 @@
   <sheetData>
     <row r="1" spans="1:57">
       <c r="A1" s="1" t="s">
-        <v>1980</v>
+        <v>1992</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1981</v>
+        <v>1993</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1982</v>
+        <v>1994</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1983</v>
+        <v>1995</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1984</v>
+        <v>1996</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1985</v>
+        <v>1997</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1986</v>
+        <v>1998</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1987</v>
+        <v>1999</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>1988</v>
+        <v>2000</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1989</v>
+        <v>2001</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1990</v>
+        <v>2002</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>1991</v>
+        <v>2003</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1992</v>
+        <v>2004</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1993</v>
+        <v>2005</v>
       </c>
       <c r="O1" s="7" t="s">
-        <v>1994</v>
+        <v>2006</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>1995</v>
+        <v>2007</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>1996</v>
+        <v>2008</v>
       </c>
       <c r="R1" s="7" t="s">
-        <v>1997</v>
+        <v>2009</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>1998</v>
+        <v>2010</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>1999</v>
+        <v>2011</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>2000</v>
+        <v>2012</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>2001</v>
+        <v>2013</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>2002</v>
+        <v>2014</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>2003</v>
+        <v>2015</v>
       </c>
       <c r="Y1" s="7" t="s">
-        <v>2004</v>
+        <v>2016</v>
       </c>
       <c r="Z1" s="7" t="s">
-        <v>2005</v>
+        <v>2017</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>2006</v>
+        <v>2018</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>2007</v>
+        <v>2019</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>2008</v>
+        <v>2020</v>
       </c>
       <c r="AD1" s="7" t="s">
-        <v>2009</v>
+        <v>2021</v>
       </c>
       <c r="AE1" s="7" t="s">
-        <v>2010</v>
+        <v>2022</v>
       </c>
       <c r="AF1" s="7" t="s">
-        <v>2011</v>
+        <v>2023</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>2013</v>
+        <v>2025</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>2014</v>
+        <v>2026</v>
       </c>
       <c r="AJ1" s="7" t="s">
-        <v>2015</v>
+        <v>2027</v>
       </c>
       <c r="AK1" s="7" t="s">
-        <v>2016</v>
+        <v>2028</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>2017</v>
+        <v>2029</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>2018</v>
+        <v>2030</v>
       </c>
       <c r="AN1" s="1" t="s">
-        <v>2019</v>
+        <v>2031</v>
       </c>
       <c r="AO1" s="7" t="s">
-        <v>2020</v>
+        <v>2032</v>
       </c>
       <c r="AP1" s="7" t="s">
-        <v>2021</v>
+        <v>2033</v>
       </c>
       <c r="AQ1" s="7" t="s">
-        <v>2022</v>
+        <v>2034</v>
       </c>
       <c r="AR1" s="1" t="s">
-        <v>2023</v>
+        <v>2035</v>
       </c>
       <c r="AS1" s="1" t="s">
-        <v>2024</v>
+        <v>2036</v>
       </c>
       <c r="AT1" s="1" t="s">
-        <v>2025</v>
+        <v>2037</v>
       </c>
       <c r="AU1" s="1" t="s">
-        <v>2026</v>
+        <v>2038</v>
       </c>
       <c r="AV1" s="1" t="s">
-        <v>2027</v>
+        <v>2039</v>
       </c>
       <c r="AW1" s="1" t="s">
-        <v>2028</v>
+        <v>2040</v>
       </c>
       <c r="AX1" s="1" t="s">
-        <v>2029</v>
+        <v>2041</v>
       </c>
       <c r="AY1" s="1" t="s">
-        <v>2030</v>
+        <v>2042</v>
       </c>
       <c r="AZ1" s="7" t="s">
-        <v>2031</v>
+        <v>2043</v>
       </c>
       <c r="BA1" s="1" t="s">
-        <v>2032</v>
+        <v>2044</v>
       </c>
       <c r="BB1" s="1" t="s">
-        <v>2033</v>
+        <v>2045</v>
       </c>
       <c r="BC1" s="7" t="s">
-        <v>2034</v>
+        <v>2046</v>
       </c>
       <c r="BD1" s="1" t="s">
-        <v>2035</v>
+        <v>2047</v>
       </c>
       <c r="BE1" s="1" t="s">
-        <v>2036</v>
+        <v>2048</v>
       </c>
     </row>
     <row r="2" spans="1:57">
@@ -61595,6 +61631,173 @@
       </c>
       <c r="BE331" t="s">
         <v>1979</v>
+      </c>
+    </row>
+    <row r="332" spans="1:57">
+      <c r="A332" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B332" t="s">
+        <v>1</v>
+      </c>
+      <c r="C332" t="s">
+        <v>1981</v>
+      </c>
+      <c r="D332" s="2">
+        <v>46191.81028935185185 </v>
+      </c>
+      <c r="E332" t="s">
+        <v>3</v>
+      </c>
+      <c r="F332" t="s">
+        <v>3</v>
+      </c>
+      <c r="G332" t="s">
+        <v>5</v>
+      </c>
+      <c r="H332" t="s">
+        <v>1982</v>
+      </c>
+      <c r="I332" s="3">
+        <v>25</v>
+      </c>
+      <c r="J332" s="4">
+        <v>46191</v>
+      </c>
+      <c r="K332" s="5">
+        <v>0.81028935185185</v>
+      </c>
+      <c r="L332" t="s">
+        <v>1983</v>
+      </c>
+      <c r="M332" t="s">
+        <v>8</v>
+      </c>
+      <c r="N332" t="s">
+        <v>233</v>
+      </c>
+      <c r="O332" s="3">
+        <v>25</v>
+      </c>
+      <c r="P332" s="6">
+        <v>270.093</v>
+      </c>
+      <c r="Q332" s="6">
+        <v>6752.325</v>
+      </c>
+      <c r="R332" t="s">
+        <v>10</v>
+      </c>
+      <c r="S332" s="4">
+        <v>46191</v>
+      </c>
+      <c r="T332" s="4"/>
+      <c r="U332" t="s">
+        <v>11</v>
+      </c>
+      <c r="V332" t="s">
+        <v>12</v>
+      </c>
+      <c r="W332" s="4"/>
+      <c r="X332" s="5">
+        <v>0 </v>
+      </c>
+      <c r="Y332" s="3">
+        <v>25</v>
+      </c>
+      <c r="Z332" t="s">
+        <v>12</v>
+      </c>
+      <c r="AA332" s="4"/>
+      <c r="AB332" s="5">
+        <v>0 </v>
+      </c>
+      <c r="AC332" t="s">
+        <v>12</v>
+      </c>
+      <c r="AD332" t="s">
+        <v>12</v>
+      </c>
+      <c r="AE332" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF332" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG332" t="s">
+        <v>12</v>
+      </c>
+      <c r="AH332" t="s">
+        <v>1984</v>
+      </c>
+      <c r="AI332" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ332" t="s">
+        <v>16</v>
+      </c>
+      <c r="AK332" t="s">
+        <v>17</v>
+      </c>
+      <c r="AL332" t="s">
+        <v>1985</v>
+      </c>
+      <c r="AM332" t="s">
+        <v>1986</v>
+      </c>
+      <c r="AN332" t="s">
+        <v>20</v>
+      </c>
+      <c r="AO332" s="6">
+        <v>25.000</v>
+      </c>
+      <c r="AP332" t="s">
+        <v>21</v>
+      </c>
+      <c r="AQ332" t="s">
+        <v>22</v>
+      </c>
+      <c r="AR332" t="s">
+        <v>23</v>
+      </c>
+      <c r="AS332" t="s">
+        <v>47</v>
+      </c>
+      <c r="AT332" s="4">
+        <v>46191</v>
+      </c>
+      <c r="AU332" t="s">
+        <v>1987</v>
+      </c>
+      <c r="AV332" t="s">
+        <v>1988</v>
+      </c>
+      <c r="AW332" t="s">
+        <v>1989</v>
+      </c>
+      <c r="AX332" t="s">
+        <v>142</v>
+      </c>
+      <c r="AY332" t="s">
+        <v>12</v>
+      </c>
+      <c r="AZ332" s="3">
+        <v>25</v>
+      </c>
+      <c r="BA332" t="s">
+        <v>29</v>
+      </c>
+      <c r="BB332" t="s">
+        <v>30</v>
+      </c>
+      <c r="BC332" t="s">
+        <v>31</v>
+      </c>
+      <c r="BD332" t="s">
+        <v>1990</v>
+      </c>
+      <c r="BE332" t="s">
+        <v>1991</v>
       </c>
     </row>
   </sheetData>
